--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125706983</v>
       </c>
       <c r="B3" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125706983</v>
       </c>
       <c r="B3" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125706983</v>
       </c>
       <c r="B3" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46645-2019 artfynd.xlsx
+++ b/artfynd/A 46645-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125706987</v>
       </c>
       <c r="B2" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125706983</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125706956</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
